--- a/data/trans_camb/P59A-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P59A-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 11,85</t>
+          <t>-8,85; 11,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,66; 0,54</t>
+          <t>-17,05; 0,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 10,19</t>
+          <t>-8,33; 10,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 18,05</t>
+          <t>-2,7; 20,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 10,38</t>
+          <t>-8,5; 9,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 11,36</t>
+          <t>-4,39; 11,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 12,14</t>
+          <t>-3,07; 11,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 2,69</t>
+          <t>-10,08; 2,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 8,43</t>
+          <t>-4,66; 8,58</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-32,6; 72,98</t>
+          <t>-33,14; 70,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,5; 5,44</t>
+          <t>-62,78; 4,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-32,05; 62,1</t>
+          <t>-32,4; 71,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,83; 142,07</t>
+          <t>-15,15; 173,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,74; 93,44</t>
+          <t>-40,16; 77,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,27; 92,65</t>
+          <t>-21,62; 105,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 73,44</t>
+          <t>-13,7; 72,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,56; 16,67</t>
+          <t>-44,02; 16,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-17,08; 56,27</t>
+          <t>-20,03; 54,19</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 9,52</t>
+          <t>-9,62; 9,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,65; 29,59</t>
+          <t>7,37; 29,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 8,02</t>
+          <t>-11,29; 6,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 9,94</t>
+          <t>-11,72; 9,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 3,74</t>
+          <t>-14,47; 4,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 6,58</t>
+          <t>-10,93; 5,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 5,65</t>
+          <t>-8,49; 5,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 12,79</t>
+          <t>-1,65; 12,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 3,32</t>
+          <t>-8,92; 3,67</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-46,89; 82,97</t>
+          <t>-47,29; 102,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,9; 269,58</t>
+          <t>31,04; 278,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-51,78; 80,6</t>
+          <t>-54,82; 58,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,17; 56,76</t>
+          <t>-42,52; 48,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,66; 20,77</t>
+          <t>-50,38; 24,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,28; 38,27</t>
+          <t>-38,4; 31,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,81; 32,68</t>
+          <t>-37,12; 35,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 75,01</t>
+          <t>-7,32; 77,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-38,38; 18,51</t>
+          <t>-37,2; 23,14</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 11,0</t>
+          <t>-8,0; 10,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 8,04</t>
+          <t>-12,01; 7,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 12,2</t>
+          <t>-8,52; 13,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 22,18</t>
+          <t>0,25; 22,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 22,51</t>
+          <t>-2,61; 22,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 13,91</t>
+          <t>-5,58; 13,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 10,58</t>
+          <t>-4,0; 11,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 9,23</t>
+          <t>-7,4; 9,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 10,3</t>
+          <t>-6,03; 10,28</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,15; 70,96</t>
+          <t>-29,74; 69,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-45,25; 54,59</t>
+          <t>-43,98; 46,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-31,74; 79,22</t>
+          <t>-32,08; 79,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 994,99</t>
+          <t>-7,23; 1091,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,1; 1000,38</t>
+          <t>-31,97; 1046,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-55,88; 802,11</t>
+          <t>-57,18; 719,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,76; 74,62</t>
+          <t>-18,03; 84,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,27; 69,3</t>
+          <t>-33,07; 64,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-27,57; 85,5</t>
+          <t>-28,54; 77,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 8,34</t>
+          <t>-2,57; 7,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 12,13</t>
+          <t>1,42; 12,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 9,28</t>
+          <t>-2,46; 8,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,62; 16,35</t>
+          <t>4,45; 16,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,89; 13,67</t>
+          <t>2,61; 13,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 10,97</t>
+          <t>0,72; 10,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 10,04</t>
+          <t>1,81; 10,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,27; 11,38</t>
+          <t>2,78; 10,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 8,32</t>
+          <t>0,07; 8,41</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 61,45</t>
+          <t>-14,6; 61,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,5; 88,83</t>
+          <t>7,63; 93,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 66,39</t>
+          <t>-13,0; 65,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30,23; 182,99</t>
+          <t>27,15; 190,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,76; 150,24</t>
+          <t>15,06; 159,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,35; 113,13</t>
+          <t>4,09; 112,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,76; 80,11</t>
+          <t>10,22; 83,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,55; 90,99</t>
+          <t>17,26; 87,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 68,1</t>
+          <t>0,02; 65,88</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 7,3</t>
+          <t>-6,25; 8,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 10,49</t>
+          <t>-4,29; 10,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 7,73</t>
+          <t>-7,18; 7,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 6,98</t>
+          <t>-7,25; 6,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 8,55</t>
+          <t>-5,31; 8,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 2,62</t>
+          <t>-11,43; 2,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 5,67</t>
+          <t>-4,78; 5,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 7,76</t>
+          <t>-2,22; 7,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 2,71</t>
+          <t>-8,08; 2,37</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-37,18; 70,75</t>
+          <t>-35,79; 87,76</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-26,01; 106,54</t>
+          <t>-23,94; 102,16</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-45,37; 77,35</t>
+          <t>-39,59; 77,19</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-36,31; 74,43</t>
+          <t>-39,04; 68,71</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-28,05; 90,02</t>
+          <t>-29,99; 79,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-63,07; 26,78</t>
+          <t>-64,16; 20,53</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 52,58</t>
+          <t>-28,72; 50,07</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 69,85</t>
+          <t>-13,5; 72,03</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-46,07; 24,49</t>
+          <t>-47,34; 19,51</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,0</t>
+          <t>-1,66; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,77; 5,04</t>
+          <t>0,71; 4,71</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 7,51</t>
+          <t>-0,02; 7,32</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 3,61</t>
+          <t>-1,22; 3,25</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,09; 5,18</t>
+          <t>0,08; 5,12</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 6,4</t>
+          <t>-0,2; 6,01</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,27</t>
+          <t>-0,8; 2,25</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,12</t>
+          <t>0,65; 4,22</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,28; 5,25</t>
+          <t>0,45; 4,92</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-34,97; 186,2</t>
+          <t>-33,28; 180,18</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 244,1</t>
+          <t>-1,11; 258,63</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 306,96</t>
+          <t>-13,25; 276,8</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-31,02; 156,06</t>
+          <t>-30,9; 176,97</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>14,11; 280,82</t>
+          <t>21,53; 329,76</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6,84; 360,62</t>
+          <t>12,46; 359,88</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 4,65</t>
+          <t>-1,06; 4,9</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,86</t>
+          <t>1,15; 6,79</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 5,78</t>
+          <t>-0,8; 5,15</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,53; 6,56</t>
+          <t>1,56; 6,55</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,54; 6,21</t>
+          <t>1,42; 6,53</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 5,15</t>
+          <t>0,4; 5,13</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,98</t>
+          <t>1,2; 5,06</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,81</t>
+          <t>2,11; 5,97</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,74</t>
+          <t>0,83; 4,83</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 38,19</t>
+          <t>-7,35; 38,29</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>7,4; 58,16</t>
+          <t>7,03; 55,14</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 47,7</t>
+          <t>-5,61; 41,37</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13,27; 73,23</t>
+          <t>13,09; 72,12</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>13,66; 70,0</t>
+          <t>12,95; 72,62</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 58,06</t>
+          <t>3,49; 54,76</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,11; 45,14</t>
+          <t>9,67; 46,94</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>15,19; 53,93</t>
+          <t>16,3; 55,96</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>6,75; 44,32</t>
+          <t>6,88; 45,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P59A-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P59A-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,03</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,81</t>
+          <t>3,35</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,2</t>
+          <t>1,64</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 11,53</t>
+          <t>-8,39; 11,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 0,54</t>
+          <t>-17,47; 0,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 10,98</t>
+          <t>-8,99; 10,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 20,24</t>
+          <t>-2,79; 18,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 9,04</t>
+          <t>-9,1; 9,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 11,96</t>
+          <t>-5,49; 10,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 11,45</t>
+          <t>-3,16; 12,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 2,53</t>
+          <t>-10,19; 2,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 8,58</t>
+          <t>-4,94; 7,85</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,14; 70,34</t>
+          <t>-31,63; 74,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,78; 4,68</t>
+          <t>-61,82; 5,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-32,4; 71,06</t>
+          <t>-35,09; 65,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 173,71</t>
+          <t>-16,7; 162,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,16; 77,65</t>
+          <t>-40,7; 82,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,62; 105,54</t>
+          <t>-22,9; 97,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 72,45</t>
+          <t>-13,78; 75,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,02; 16,65</t>
+          <t>-44,79; 18,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 54,19</t>
+          <t>-21,77; 50,34</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,72</t>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,37</t>
+          <t>-2,44</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,73</t>
+          <t>-1,88</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 9,98</t>
+          <t>-9,88; 9,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,37; 29,85</t>
+          <t>8,36; 30,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 6,19</t>
+          <t>-8,98; 9,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 9,09</t>
+          <t>-11,55; 10,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 4,56</t>
+          <t>-15,69; 3,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 5,69</t>
+          <t>-11,84; 5,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 5,97</t>
+          <t>-7,94; 6,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 12,71</t>
+          <t>-1,85; 12,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 3,67</t>
+          <t>-8,01; 4,3</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-10,83%</t>
+          <t>-0,57%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-10,11%</t>
+          <t>-10,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-13,49%</t>
+          <t>-9,31%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-47,29; 102,89</t>
+          <t>-47,71; 86,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,04; 278,42</t>
+          <t>32,89; 266,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,82; 58,04</t>
+          <t>-43,72; 80,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-42,52; 48,1</t>
+          <t>-40,68; 56,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,38; 24,64</t>
+          <t>-54,86; 18,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,4; 31,78</t>
+          <t>-42,06; 29,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,12; 35,4</t>
+          <t>-34,06; 36,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 77,91</t>
+          <t>-8,48; 76,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-37,2; 23,14</t>
+          <t>-33,39; 26,9</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,08</t>
+          <t>1,6</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>5,57</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>1,61</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 10,31</t>
+          <t>-8,21; 10,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 7,14</t>
+          <t>-12,29; 6,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 13,39</t>
+          <t>-8,31; 12,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 22,46</t>
+          <t>0,02; 21,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 22,22</t>
+          <t>-2,13; 22,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 13,88</t>
+          <t>-4,15; 15,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 11,18</t>
+          <t>-3,87; 10,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 9,11</t>
+          <t>-7,4; 8,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 10,28</t>
+          <t>-5,86; 9,52</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,74; 69,08</t>
+          <t>-31,23; 68,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-43,98; 46,26</t>
+          <t>-46,66; 41,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-32,08; 79,91</t>
+          <t>-32,09; 78,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 1091,75</t>
+          <t>-21,14; 1052,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,97; 1046,41</t>
+          <t>-34,94; 964,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-57,18; 719,04</t>
+          <t>-47,88; 787,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 84,39</t>
+          <t>-19,29; 82,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,07; 64,71</t>
+          <t>-33,3; 61,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-28,54; 77,17</t>
+          <t>-27,2; 65,26</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,09</t>
+          <t>3,84</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,84</t>
+          <t>6,71</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,27</t>
+          <t>5,06</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 7,91</t>
+          <t>-3,17; 7,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 12,44</t>
+          <t>1,11; 12,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 8,77</t>
+          <t>-1,56; 9,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,45; 16,27</t>
+          <t>3,89; 16,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,61; 13,89</t>
+          <t>2,16; 13,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 10,68</t>
+          <t>1,26; 12,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 10,53</t>
+          <t>1,69; 9,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 10,73</t>
+          <t>3,47; 10,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 8,41</t>
+          <t>1,15; 9,08</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 61,13</t>
+          <t>-16,73; 54,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,63; 93,59</t>
+          <t>5,67; 90,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 65,57</t>
+          <t>-8,41; 69,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27,15; 190,48</t>
+          <t>25,51; 175,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,06; 159,79</t>
+          <t>13,9; 146,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,09; 112,68</t>
+          <t>7,56; 126,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,22; 83,94</t>
+          <t>9,81; 76,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,26; 87,23</t>
+          <t>21,06; 91,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,02; 65,88</t>
+          <t>6,76; 72,95</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>-0,93</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,8</t>
+          <t>-1,61</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,33</t>
+          <t>-1,33</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 8,65</t>
+          <t>-7,47; 7,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 10,46</t>
+          <t>-3,71; 10,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 7,92</t>
+          <t>-8,89; 6,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 6,67</t>
+          <t>-7,21; 6,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 8,07</t>
+          <t>-4,98; 8,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 2,26</t>
+          <t>-8,13; 3,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 5,24</t>
+          <t>-4,54; 5,41</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 7,9</t>
+          <t>-2,44; 7,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 2,37</t>
+          <t>-6,22; 3,4</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>-6,51%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-28,27%</t>
+          <t>-12,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-16,89%</t>
+          <t>-9,64%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-35,79; 87,76</t>
+          <t>-38,91; 74,7</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-23,94; 102,16</t>
+          <t>-19,85; 104,26</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-39,59; 77,19</t>
+          <t>-47,72; 65,58</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-39,04; 68,71</t>
+          <t>-42,11; 66,44</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-29,99; 79,1</t>
+          <t>-26,99; 86,85</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-64,16; 20,53</t>
+          <t>-45,74; 40,54</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 50,07</t>
+          <t>-27,8; 54,84</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 72,03</t>
+          <t>-14,15; 70,02</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-47,34; 19,51</t>
+          <t>-35,93; 31,14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,85</t>
+          <t>2,48</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,66</t>
+          <t>2,35</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,35</t>
+          <t>2,44</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,0</t>
+          <t>-1,48; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,71</t>
+          <t>0,57; 4,8</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 7,32</t>
+          <t>0,21; 7,68</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,25</t>
+          <t>-1,15; 3,53</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,08; 5,12</t>
+          <t>0,06; 5,12</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 6,01</t>
+          <t>-0,17; 5,56</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 2,25</t>
+          <t>-0,87; 2,16</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,22</t>
+          <t>0,8; 4,24</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,92</t>
+          <t>0,22; 5,07</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>624,71%</t>
+          <t>837,06%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>114,41%</t>
+          <t>118,8%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-33,28; 180,18</t>
+          <t>-31,83; 175,46</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 258,63</t>
+          <t>-0,41; 246,8</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 276,8</t>
+          <t>-13,2; 300,65</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-30,9; 176,97</t>
+          <t>-34,56; 158,76</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>21,53; 329,76</t>
+          <t>21,98; 325,46</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>12,46; 359,88</t>
+          <t>-0,15; 347,75</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,57</t>
+          <t>2,91</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,87</t>
+          <t>3,53</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,72</t>
+          <t>3,24</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 4,9</t>
+          <t>-0,86; 4,87</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,15; 6,79</t>
+          <t>1,26; 6,93</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 5,15</t>
+          <t>0,12; 5,94</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,55</t>
+          <t>1,49; 6,71</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,42; 6,53</t>
+          <t>1,54; 6,21</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,4; 5,13</t>
+          <t>1,24; 5,74</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,06</t>
+          <t>1,04; 4,81</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,97</t>
+          <t>2,17; 5,95</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,83</t>
+          <t>1,22; 4,98</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 38,29</t>
+          <t>-5,68; 40,97</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>7,03; 55,14</t>
+          <t>8,11; 58,84</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 41,37</t>
+          <t>0,82; 48,81</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13,09; 72,12</t>
+          <t>14,27; 75,34</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>12,95; 72,62</t>
+          <t>13,88; 71,88</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,49; 54,76</t>
+          <t>10,41; 63,57</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,67; 46,94</t>
+          <t>7,64; 43,62</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>16,3; 55,96</t>
+          <t>17,1; 55,27</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>6,88; 45,33</t>
+          <t>9,99; 45,49</t>
         </is>
       </c>
     </row>
